--- a/nr-update-med-administration-descr/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/nr-update-med-administration-descr/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-09T09:28:23+00:00</t>
+    <t>2024-09-09T09:28:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil se basant sur la ressource Medication Administration pour indiquer l'oxygène inhalé. Ce profil permet de compléter les informations de la ressource Observation saturation en oxygène avec les les apports d'oxygène via une ventilation mécanique.</t>
+    <t>Profil se basant sur la ressource Medication Administration pour indiquer l'oxygène inhalé. Ce profil permet de compléter les informations de la ressource Observation saturation en oxygène avec les apports d'oxygène via une ventilation mécanique.</t>
   </si>
   <si>
     <t>Purpose</t>
